--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E173D6A-FFC0-48CA-A3E3-02D3751184DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E494A-33C0-4DC0-B7A6-773F8C763292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -95,9 +95,6 @@
     <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?v=1786718127215</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?v=1786718127215</t>
-  </si>
-  <si>
     <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/pib_gasto_2018.xlsx?v=1786718144939</t>
   </si>
   <si>
@@ -111,6 +108,9 @@
   </si>
   <si>
     <t>Expansion/Contraccion</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?v=1786988019214</t>
   </si>
 </sst>
 </file>
@@ -525,7 +525,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -538,7 +538,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -557,7 +557,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -565,7 +565,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -573,7 +573,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -581,7 +581,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4E494A-33C0-4DC0-B7A6-773F8C763292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097EAA3C-0C0C-4438-92B5-47E0BAAD299E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Tasas</t>
   </si>
@@ -53,15 +53,6 @@
     <t>Fiscal</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/tbm_activad.xlsx?v=1786655129161?v=1786655129162</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-cambiario/documents/TASA_DOLAR_REFERENCIA_MC.xlsx?v=1786659910185</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/documents/Operaciones_Mensual.xlsx?v=1786660033322</t>
-  </si>
-  <si>
     <t>Llegada</t>
   </si>
   <si>
@@ -89,38 +80,61 @@
     <t>link</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/Tasas_Interbancarias_Promedio_por_Plazos.xlsm?v=1786718108139</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?v=1786718127215</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/pib_gasto_2018.xlsx?v=1786718144939</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/imae_2018.xlsx?v=1786718144939</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/precios/documents/ipc_base_2019-2020.xls?v=1786718159185</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-turismo/documents/lleg_total.xls?v=1786718170603</t>
-  </si>
-  <si>
     <t>Expansion/Contraccion</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?v=1786988019214</t>
+    <t>ENCFT</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/documents/Operaciones_Mensual.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-turismo/documents/lleg_total.xls?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/pib_gasto_2018.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/imae_2018.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/precios/documents/ipc_base_2019-2020.xls?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-de-trabajo/documents/00_Indicadores.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/Tasas_Interbancarias_Promedio_por_Plazos.xlsm?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-cambiario/documents/TASA_DOLAR_REFERENCIA_MC.xlsx?</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/tbm_activad.xlsx?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,13 +157,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -482,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -490,55 +507,55 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
-        <v>5</v>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>2</v>
@@ -548,43 +565,63 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
-        <v>6</v>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>18</v>
+        <v>5</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" t="s">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>20</v>
+        <v>7</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{9DE02037-6ECF-4DD4-82F2-961B3FFE5851}"/>
+    <hyperlink ref="B8" r:id="rId2" xr:uid="{00A0E442-5739-43D1-8FB6-D3C8F9015A0B}"/>
+    <hyperlink ref="B9" r:id="rId3" xr:uid="{3791D548-9C3D-4537-AC40-B1632A6D0758}"/>
+    <hyperlink ref="B10" r:id="rId4" xr:uid="{C6676FFB-2A07-4920-A2D0-05EEB685A83B}"/>
+    <hyperlink ref="B11" r:id="rId5" xr:uid="{285A6544-5F76-4F03-8FFE-73B3F7DEE87B}"/>
+    <hyperlink ref="B12" r:id="rId6" xr:uid="{C89394F0-3D04-454C-AF00-37D33A259B6A}"/>
+    <hyperlink ref="B13" r:id="rId7" xr:uid="{912043EE-8631-4034-8D70-39B5A1BEEEA7}"/>
+    <hyperlink ref="B4" r:id="rId8" xr:uid="{AD6317BC-8F5C-4D59-91DE-D6B0B732EFFD}"/>
+    <hyperlink ref="B3" r:id="rId9" xr:uid="{AA5AA6A9-C0C1-437A-8891-A139E49A1AF1}"/>
+    <hyperlink ref="B2" r:id="rId10" xr:uid="{41C7D673-5E0B-419F-A990-053EE7C3D402}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{097EAA3C-0C0C-4438-92B5-47E0BAAD299E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7799E83A-B170-4368-9A0B-E2A83CE9E245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>Tipo de cambio</t>
   </si>
   <si>
-    <t>https://www.bancentral.gov.do/a/d/2714-facilidades-permanentes-de-contraccion-y-expansion-monetaria-a-plazo-de-un-dia</t>
-  </si>
-  <si>
     <t>Fiscal</t>
   </si>
   <si>
@@ -86,37 +83,40 @@
     <t>ENCFT</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/documents/Operaciones_Mensual.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-turismo/documents/lleg_total.xls?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/pib_gasto_2018.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/imae_2018.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/precios/documents/ipc_base_2019-2020.xls?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-de-trabajo/documents/00_Indicadores.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/Tasas_Interbancarias_Promedio_por_Plazos.xlsm?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-cambiario/documents/TASA_DOLAR_REFERENCIA_MC.xlsx?</t>
-  </si>
-  <si>
-    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/tbm_activad.xlsx?</t>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?v=1787068738113</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?v=1787068738113</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/tbm_activad.xlsx?v=1787068953297?v=1787068953298</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-cambiario/documents/TASA_DOLAR_REFERENCIA_MC.xlsx?v=1787068969171</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-monetario-y-financiero/documents/Tasas_Interbancarias_Promedio_por_Plazos.xlsm?v=1787068979323</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/instrumentos-de-inversion/instrumentos-operaciones-de-mercado-abierto/documents/Resultados_Contraccion_Expansion.xlsm?v=1787069004470</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/documents/Operaciones_Mensual.xlsx?v=1787069023325</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-turismo/documents/lleg_total.xls?v=1787069095184</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/pib_2018.xlsx?v=1787069109089</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/sector-real/documents/imae_2018.xlsx?v=1787069109089</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/precios/documents/ipc_base_2019-2020.xls?v=1787069138883</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-de-trabajo/documents/00_Indicadores.xlsx?v=1787069150098</t>
   </si>
 </sst>
 </file>
@@ -507,10 +507,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -518,7 +518,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -526,102 +526,90 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{9DE02037-6ECF-4DD4-82F2-961B3FFE5851}"/>
-    <hyperlink ref="B8" r:id="rId2" xr:uid="{00A0E442-5739-43D1-8FB6-D3C8F9015A0B}"/>
-    <hyperlink ref="B9" r:id="rId3" xr:uid="{3791D548-9C3D-4537-AC40-B1632A6D0758}"/>
-    <hyperlink ref="B10" r:id="rId4" xr:uid="{C6676FFB-2A07-4920-A2D0-05EEB685A83B}"/>
-    <hyperlink ref="B11" r:id="rId5" xr:uid="{285A6544-5F76-4F03-8FFE-73B3F7DEE87B}"/>
-    <hyperlink ref="B12" r:id="rId6" xr:uid="{C89394F0-3D04-454C-AF00-37D33A259B6A}"/>
-    <hyperlink ref="B13" r:id="rId7" xr:uid="{912043EE-8631-4034-8D70-39B5A1BEEEA7}"/>
-    <hyperlink ref="B4" r:id="rId8" xr:uid="{AD6317BC-8F5C-4D59-91DE-D6B0B732EFFD}"/>
-    <hyperlink ref="B3" r:id="rId9" xr:uid="{AA5AA6A9-C0C1-437A-8891-A139E49A1AF1}"/>
-    <hyperlink ref="B2" r:id="rId10" xr:uid="{41C7D673-5E0B-419F-A990-053EE7C3D402}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7799E83A-B170-4368-9A0B-E2A83CE9E245}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B52B7EB-950A-4BBB-87A3-71F5CF44BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Tasas</t>
   </si>
@@ -117,6 +117,114 @@
   </si>
   <si>
     <t>https://cdn.bancentral.gov.do/documents/estadisticas/mercado-de-trabajo/documents/00_Indicadores.xlsx?v=1787069150098</t>
+  </si>
+  <si>
+    <t>IBC Brasil</t>
+  </si>
+  <si>
+    <t>https://www.bcb.gov.br/content/indeco/indicadoresselecionados/ies-01.xlsx</t>
+  </si>
+  <si>
+    <t>blob:https://www.bcb.gov.br/b5f58f78-2c73-4a4c-b551-8fdb85346741</t>
+  </si>
+  <si>
+    <t>TPM Brasil</t>
+  </si>
+  <si>
+    <t>TPM Chile</t>
+  </si>
+  <si>
+    <t>https://si3.bcentral.cl/Indicadoressiete/secure/Serie.aspx?gcode=TPM&amp;param=VwAuAEMAdgBMAC4AcgBkADgALQBoADIAZABfADAAMAAzADIAYQBWAGMANABIAFoAaQBUAEsANgA2AHQAOQBHAFMAQQBrAFkAdAB5AEsATABrAHAAeQB1AEcAIwBFAEEAZAA2AE8AQgB1ADcATwB1ADQANwBoAHQAcQBnAHUATAAzAG4AbQBrAHYASwBWAGoAcQB1AHAAVgBzADIANwA2AGYAVABkAGsAQQBOAEoAVQBNAEgAUwBGAHYAeABNAGEA</t>
+  </si>
+  <si>
+    <t>https://si3.bcentral.cl/Indicadoressiete/secure/Serie.aspx?gcode=IMC_EP03_YTYPCT&amp;param=TwBiAFUARwBXAGIAbQB3AE4ALQA5AEsAdwAjAE0ATQBBAEsAZgBrADUAaAAxAF8AdQBTAHoAMgAyAHgAWABvAFAAOAAuAFoAQgBCAHoAcABTAHIAQgBpAHQAMABzAHQAMwBRAGwATgBNAEEASgBnAHgAQQBWAFIAdQAuADMAYgBzAGQAYwBPAHgAcQBIAGYAOAB3AFYAQQBuAGQATwA5AEUAYwBKADQAVwBUAEwAYwB5AFMAbgBNADEASwBkAG8AdABCADkAdQB1AHkAQQBTAFAA</t>
+  </si>
+  <si>
+    <t>IMACEC Chile</t>
+  </si>
+  <si>
+    <t>IPC Colombia</t>
+  </si>
+  <si>
+    <t>blob:https://suameca.banrep.gov.co/007dfad7-9d7b-43c0-baeb-5fc9df12f39c</t>
+  </si>
+  <si>
+    <t>TPM Colombia</t>
+  </si>
+  <si>
+    <t>blob:https://suameca.banrep.gov.co/17f2467c-1214-4133-8cd7-52d67a0fab5b</t>
+  </si>
+  <si>
+    <t>https://www.dane.gov.co/files/operaciones/ISE/bol-ISE-jun2026.pdf</t>
+  </si>
+  <si>
+    <t>IMAE Colombia</t>
+  </si>
+  <si>
+    <t>IPC Brasil</t>
+  </si>
+  <si>
+    <t>IPC Chile</t>
+  </si>
+  <si>
+    <t>blob:https://www.bcb.gov.br/42c04283-2e93-48a8-a22b-966ed239dbd5</t>
+  </si>
+  <si>
+    <t>https://si3.bcentral.cl/Indicadoressiete/secure/Serie.aspx?gcode=IPC&amp;param=UQBSAEYAYwAxAFIARABYADAALQBqAHAAWABKAHEAcQBzAHAAQgB4ADcATwBHAGIAMgBfAEwATgBOAHIAWQA1ACMAZwBsAC4AeABtAEwATQBsAHcAdQBvAGQARwBQAGUARQBvAG0ASwB4AEQAbABTAGgARgAxAGUAQgBxAHkAcwA5AG8ARQAzAGgAMQBPAFQARgBSAEwASABZAE0ARgBKAFoAMwBmAHYATgBoAGMANQBpAE8ANwBFAGMAJAA%3d</t>
+  </si>
+  <si>
+    <t>https://banguat.gob.gt/sites/default/files/banguat/Publica/IMAE/2013/Cuadros_y_gr%C3%A1ficas_IMAE_jun2026.xlsx</t>
+  </si>
+  <si>
+    <t>IMAE Guatemala</t>
+  </si>
+  <si>
+    <t>https://banguat.gob.gt/sites/default/files/banguat/Publica/Prensa/boletin_tasa_int240626.pdf</t>
+  </si>
+  <si>
+    <t>TPM Guatemala</t>
+  </si>
+  <si>
+    <t>IPC Guatemala</t>
+  </si>
+  <si>
+    <t>https://banguat.gob.gt/sites/default/files/banguat/estaeco/SR/sr005.xls</t>
+  </si>
+  <si>
+    <t>IPC Paraguay</t>
+  </si>
+  <si>
+    <t>https://www.bcp.gov.py/documents/20117/2567893/IPC_desde_1950_Empalmada_a_4_agrupaciones_Web+BCP+PE.xlsx/045f799c-1e77-8959-c220-490520b31195?t=1785773925220</t>
+  </si>
+  <si>
+    <t>IPC Perú</t>
+  </si>
+  <si>
+    <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN38705PM%27/grupos/0/anio1/1991/anio2/2026/mes1/1/mes2/7/dia1/0/dia2/0</t>
+  </si>
+  <si>
+    <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PD04722MM%27/grupos/0/anio1/2003/anio2/2026/mes1/9/mes2/8/dia1/0/dia2/0</t>
+  </si>
+  <si>
+    <t>TPM Perú</t>
+  </si>
+  <si>
+    <t>IMAE Perú</t>
+  </si>
+  <si>
+    <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN01728AM%27/grupos/0/anio1/1995/anio2/2026/mes1/1/mes2/5/dia1/0/dia2/0</t>
+  </si>
+  <si>
+    <t>IPC Uruguay</t>
+  </si>
+  <si>
+    <t>https://www5.ine.gub.uy/documents/Estad%C3%ADsticasecon%C3%B3micas/SERIES%20Y%20OTROS/IPC/Base%20Octubre%202022=100/IPC%20gral%20y%20variaciones_base%202022.xlsx</t>
+  </si>
+  <si>
+    <t>IMAE Uruguay</t>
+  </si>
+  <si>
+    <t>https://www.bcu.gub.uy/_layouts/15/BCU.Portal2016/BCUListasHandler.ashx</t>
   </si>
 </sst>
 </file>
@@ -499,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -609,6 +717,150 @@
         <v>25</v>
       </c>
     </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>58</v>
+      </c>
+      <c r="B30" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B52B7EB-950A-4BBB-87A3-71F5CF44BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205529F8-C8D5-4F9B-8A4F-2EC04FBFB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Tasas</t>
   </si>
@@ -125,12 +125,6 @@
     <t>https://www.bcb.gov.br/content/indeco/indicadoresselecionados/ies-01.xlsx</t>
   </si>
   <si>
-    <t>blob:https://www.bcb.gov.br/b5f58f78-2c73-4a4c-b551-8fdb85346741</t>
-  </si>
-  <si>
-    <t>TPM Brasil</t>
-  </si>
-  <si>
     <t>TPM Chile</t>
   </si>
   <si>
@@ -146,30 +140,15 @@
     <t>IPC Colombia</t>
   </si>
   <si>
-    <t>blob:https://suameca.banrep.gov.co/007dfad7-9d7b-43c0-baeb-5fc9df12f39c</t>
-  </si>
-  <si>
-    <t>TPM Colombia</t>
-  </si>
-  <si>
-    <t>blob:https://suameca.banrep.gov.co/17f2467c-1214-4133-8cd7-52d67a0fab5b</t>
-  </si>
-  <si>
     <t>https://www.dane.gov.co/files/operaciones/ISE/bol-ISE-jun2026.pdf</t>
   </si>
   <si>
     <t>IMAE Colombia</t>
   </si>
   <si>
-    <t>IPC Brasil</t>
-  </si>
-  <si>
     <t>IPC Chile</t>
   </si>
   <si>
-    <t>blob:https://www.bcb.gov.br/42c04283-2e93-48a8-a22b-966ed239dbd5</t>
-  </si>
-  <si>
     <t>https://si3.bcentral.cl/Indicadoressiete/secure/Serie.aspx?gcode=IPC&amp;param=UQBSAEYAYwAxAFIARABYADAALQBqAHAAWABKAHEAcQBzAHAAQgB4ADcATwBHAGIAMgBfAEwATgBOAHIAWQA1ACMAZwBsAC4AeABtAEwATQBsAHcAdQBvAGQARwBQAGUARQBvAG0ASwB4AEQAbABTAGgARgAxAGUAQgBxAHkAcwA5AG8ARQAzAGgAMQBPAFQARgBSAEwASABZAE0ARgBKAFoAMwBmAHYATgBoAGMANQBpAE8ANwBFAGMAJAA%3d</t>
   </si>
   <si>
@@ -225,6 +204,9 @@
   </si>
   <si>
     <t>https://www.bcu.gub.uy/_layouts/15/BCU.Portal2016/BCUListasHandler.ashx</t>
+  </si>
+  <si>
+    <t>https://suameca.banrep.gov.co/estadisticas-economicas-back/rest/estadisticaEconomicaRestService/exportarReporteExcel?reportPath=/shared/Estadisticas_Banco_de_la_Republica/1_Precios_e_Inflacion/1_Inflacion_y_meta/1_Inflacion_y_meta_iqy&amp;formato=excel</t>
   </si>
 </sst>
 </file>
@@ -607,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -727,71 +709,71 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>44</v>
@@ -799,7 +781,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
         <v>46</v>
@@ -810,55 +792,31 @@
         <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" t="s">
         <v>50</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205529F8-C8D5-4F9B-8A4F-2EC04FBFB6CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34056AEF-B672-4FD0-BE11-910A03999E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Tasas</t>
   </si>
@@ -140,28 +140,10 @@
     <t>IPC Colombia</t>
   </si>
   <si>
-    <t>https://www.dane.gov.co/files/operaciones/ISE/bol-ISE-jun2026.pdf</t>
-  </si>
-  <si>
-    <t>IMAE Colombia</t>
-  </si>
-  <si>
     <t>IPC Chile</t>
   </si>
   <si>
     <t>https://si3.bcentral.cl/Indicadoressiete/secure/Serie.aspx?gcode=IPC&amp;param=UQBSAEYAYwAxAFIARABYADAALQBqAHAAWABKAHEAcQBzAHAAQgB4ADcATwBHAGIAMgBfAEwATgBOAHIAWQA1ACMAZwBsAC4AeABtAEwATQBsAHcAdQBvAGQARwBQAGUARQBvAG0ASwB4AEQAbABTAGgARgAxAGUAQgBxAHkAcwA5AG8ARQAzAGgAMQBPAFQARgBSAEwASABZAE0ARgBKAFoAMwBmAHYATgBoAGMANQBpAE8ANwBFAGMAJAA%3d</t>
-  </si>
-  <si>
-    <t>https://banguat.gob.gt/sites/default/files/banguat/Publica/IMAE/2013/Cuadros_y_gr%C3%A1ficas_IMAE_jun2026.xlsx</t>
-  </si>
-  <si>
-    <t>IMAE Guatemala</t>
-  </si>
-  <si>
-    <t>https://banguat.gob.gt/sites/default/files/banguat/Publica/Prensa/boletin_tasa_int240626.pdf</t>
-  </si>
-  <si>
-    <t>TPM Guatemala</t>
   </si>
   <si>
     <t>IPC Guatemala</t>
@@ -589,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -725,10 +707,10 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -736,39 +718,39 @@
         <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
         <v>40</v>
-      </c>
-      <c r="B21" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
         <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -789,34 +771,10 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" t="s">
         <v>48</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>53</v>
-      </c>
-      <c r="B28" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34056AEF-B672-4FD0-BE11-910A03999E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB124B13-F49B-4C70-BC4D-970854DF569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Tasas</t>
   </si>
@@ -174,12 +174,6 @@
   </si>
   <si>
     <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN01728AM%27/grupos/0/anio1/1995/anio2/2026/mes1/1/mes2/5/dia1/0/dia2/0</t>
-  </si>
-  <si>
-    <t>IPC Uruguay</t>
-  </si>
-  <si>
-    <t>https://www5.ine.gub.uy/documents/Estad%C3%ADsticasecon%C3%B3micas/SERIES%20Y%20OTROS/IPC/Base%20Octubre%202022=100/IPC%20gral%20y%20variaciones_base%202022.xlsx</t>
   </si>
   <si>
     <t>IMAE Uruguay</t>
@@ -571,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -718,7 +712,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -767,14 +761,6 @@
       </c>
       <c r="B24" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>47</v>
-      </c>
-      <c r="B25" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB124B13-F49B-4C70-BC4D-970854DF569D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5F3C4-8AC2-4DC6-A0CA-F2160F88BF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Tasas</t>
   </si>
@@ -174,12 +174,6 @@
   </si>
   <si>
     <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN01728AM%27/grupos/0/anio1/1995/anio2/2026/mes1/1/mes2/5/dia1/0/dia2/0</t>
-  </si>
-  <si>
-    <t>IMAE Uruguay</t>
-  </si>
-  <si>
-    <t>https://www.bcu.gub.uy/_layouts/15/BCU.Portal2016/BCUListasHandler.ashx</t>
   </si>
   <si>
     <t>https://suameca.banrep.gov.co/estadisticas-economicas-back/rest/estadisticaEconomicaRestService/exportarReporteExcel?reportPath=/shared/Estadisticas_Banco_de_la_Republica/1_Precios_e_Inflacion/1_Inflacion_y_meta/1_Inflacion_y_meta_iqy&amp;formato=excel</t>
@@ -565,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -712,7 +706,7 @@
         <v>32</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -753,14 +747,6 @@
       </c>
       <c r="B23" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA5F3C4-8AC2-4DC6-A0CA-F2160F88BF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF51D27-77C9-460F-B11C-0B0B535B69EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
   <si>
     <t>Tasas</t>
   </si>
@@ -137,9 +137,6 @@
     <t>IMACEC Chile</t>
   </si>
   <si>
-    <t>IPC Colombia</t>
-  </si>
-  <si>
     <t>IPC Chile</t>
   </si>
   <si>
@@ -174,9 +171,6 @@
   </si>
   <si>
     <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN01728AM%27/grupos/0/anio1/1995/anio2/2026/mes1/1/mes2/5/dia1/0/dia2/0</t>
-  </si>
-  <si>
-    <t>https://suameca.banrep.gov.co/estadisticas-economicas-back/rest/estadisticaEconomicaRestService/exportarReporteExcel?reportPath=/shared/Estadisticas_Banco_de_la_Republica/1_Precios_e_Inflacion/1_Inflacion_y_meta/1_Inflacion_y_meta_iqy&amp;formato=excel</t>
   </si>
 </sst>
 </file>
@@ -559,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D253174-613F-45DE-AC4C-3991E1527F00}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" customWidth="1"/>
@@ -695,39 +689,39 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
         <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B21" t="s">
         <v>40</v>
@@ -738,15 +732,7 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
         <v>43</v>
-      </c>
-      <c r="B23" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Links_alertas.xlsx
+++ b/Links_alertas.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\Bcfs1\PROMIECO\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\bcfs\promieco\Analisis_Monetario\Base de Datos\Insumos Bases de Datos\Automatizaciones\Alertas Telegram\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF51D27-77C9-460F-B11C-0B0B535B69EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE3A28A-D021-49C1-8EC0-63DF90C14DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26C71539-8EC0-4D01-AE2D-38C1FA926144}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>ENCFT</t>
   </si>
   <si>
-    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?v=1787068738113</t>
-  </si>
-  <si>
     <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Serie_Historica_Spread_del_EMBI.xlsx?v=1787068738113</t>
   </si>
   <si>
@@ -171,6 +168,9 @@
   </si>
   <si>
     <t>https://estadisticas.bcrp.gob.pe/estadisticas/series/excelmensuales/index/codigos/%27PN01728AM%27/grupos/0/anio1/1995/anio2/2026/mes1/1/mes2/5/dia1/0/dia2/0</t>
+  </si>
+  <si>
+    <t>https://cdn.bancentral.gov.do/documents/entorno-internacional/documents/Materias_Primas.pdf?</t>
   </si>
 </sst>
 </file>
@@ -572,7 +572,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -580,7 +580,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -588,7 +588,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -596,7 +596,7 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -604,7 +604,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -612,7 +612,7 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -620,7 +620,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -628,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -636,7 +636,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,7 +644,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -652,7 +652,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -660,79 +660,79 @@
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s">
         <v>28</v>
-      </c>
-      <c r="B16" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" t="s">
         <v>36</v>
-      </c>
-      <c r="B19" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
         <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
         <v>42</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>
